--- a/e61 Projects/DBCFT/AI_scenarios.xlsx
+++ b/e61 Projects/DBCFT/AI_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MattNolan\Git\TVHENZ\e61 Projects\DBCFT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{F00D8499-CEE8-4A06-922D-77BB799459A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{A7CBC9D9-D102-48FB-BF03-150A2F1481EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" activeTab="3" xr2:uid="{685E3FA9-E03D-4729-B280-910D29003171}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{685E3FA9-E03D-4729-B280-910D29003171}"/>
   </bookViews>
   <sheets>
     <sheet name="PBO_wage_only" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="38">
   <si>
     <t>Change Gov Tax Rev</t>
   </si>
@@ -138,13 +138,25 @@
     <t>Wage to much lower (1ppt decline)</t>
   </si>
   <si>
-    <t>Prod to much higher (0.8ppt increase)</t>
+    <t>Actual total baseline</t>
   </si>
   <si>
-    <t>Prod to much higher and wage to lower (0.8ppt and 0.5ppt respectively)</t>
+    <t>Prod to much higher (0.6ppt increase)</t>
   </si>
   <si>
-    <t>Actual total baseline</t>
+    <t>Prod to much higher and wage to lower (0.6ppt and 0.5ppt respectively)</t>
+  </si>
+  <si>
+    <t>Prod to much higher (0.3ppt increase)</t>
+  </si>
+  <si>
+    <t>Fiddle in the Prod 0.3% case</t>
+  </si>
+  <si>
+    <t>Prod_2</t>
+  </si>
+  <si>
+    <t>Prod_wage_2</t>
   </si>
 </sst>
 </file>
@@ -155,7 +167,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +186,12 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -200,7 +218,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -208,6 +226,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6176,7 +6195,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -6924,13 +6943,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F856651C-544E-49C9-99FE-8CF9CDD8CED8}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>24</v>
       </c>
@@ -6947,7 +6966,7 @@
         <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I1" t="s">
         <v>10</v>
@@ -6958,8 +6977,11 @@
       <c r="K1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -6992,7 +7014,7 @@
         <v>1.9170114419962013E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -7025,7 +7047,7 @@
         <v>5.8789404551852133E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -7058,7 +7080,7 @@
         <v>9.8588518995703141E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -7091,7 +7113,7 @@
         <v>1.3500684453341922E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -7124,7 +7146,7 @@
         <v>1.7632021526983885E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -7157,7 +7179,7 @@
         <v>2.1432231322697139E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -7190,7 +7212,7 @@
         <v>2.5177198382443037E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -7223,7 +7245,7 @@
         <v>2.8872527667694315E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -7256,7 +7278,7 @@
         <v>3.2531728928626852E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -7289,7 +7311,7 @@
         <v>3.6115806577012563E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -7322,9 +7344,388 @@
         <v>3.9700933037690483E-2</v>
       </c>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G19" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" t="s">
         <v>31</v>
+      </c>
+      <c r="I14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>1530.7281520547112</v>
+      </c>
+      <c r="D15">
+        <v>1198.7835730143124</v>
+      </c>
+      <c r="E15">
+        <v>488.03555485897232</v>
+      </c>
+      <c r="F15">
+        <v>781.4955980675004</v>
+      </c>
+      <c r="H15">
+        <v>815327</v>
+      </c>
+      <c r="I15" s="6">
+        <f>D15/$H15</f>
+        <v>1.4703101614619808E-3</v>
+      </c>
+      <c r="J15" s="6">
+        <f t="shared" ref="J15:J25" si="3">E15/$H15</f>
+        <v>5.9857646669247099E-4</v>
+      </c>
+      <c r="K15" s="6">
+        <f t="shared" ref="K15:K25" si="4">F15/$H15</f>
+        <v>9.5850572600625317E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>4238.196249053115</v>
+      </c>
+      <c r="D16">
+        <v>3505.542222820688</v>
+      </c>
+      <c r="E16">
+        <v>1178.9234878544812</v>
+      </c>
+      <c r="F16">
+        <v>2455.79420447757</v>
+      </c>
+      <c r="H16">
+        <v>836286</v>
+      </c>
+      <c r="I16" s="6">
+        <f>D16/$H16</f>
+        <v>4.1917982876918756E-3</v>
+      </c>
+      <c r="J16" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4097132892987342E-3</v>
+      </c>
+      <c r="K16" s="6">
+        <f t="shared" si="4"/>
+        <v>2.9365482675514955E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>7198.384803794208</v>
+      </c>
+      <c r="D17">
+        <v>6013.4250283007277</v>
+      </c>
+      <c r="E17">
+        <v>1962.2438004995347</v>
+      </c>
+      <c r="F17">
+        <v>4246.2234743083536</v>
+      </c>
+      <c r="H17">
+        <v>863473</v>
+      </c>
+      <c r="I17" s="6">
+        <f>D17/$H17</f>
+        <v>6.964230529849489E-3</v>
+      </c>
+      <c r="J17" s="6">
+        <f t="shared" si="3"/>
+        <v>2.2725016306236962E-3</v>
+      </c>
+      <c r="K17" s="6">
+        <f t="shared" si="4"/>
+        <v>4.9176100171150153E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>10463.685658087721</v>
+      </c>
+      <c r="D18">
+        <v>8783.8242061012425</v>
+      </c>
+      <c r="E18">
+        <v>2943.1375942567247</v>
+      </c>
+      <c r="F18">
+        <v>6120.1146767321625</v>
+      </c>
+      <c r="H18">
+        <v>910149</v>
+      </c>
+      <c r="I18" s="6">
+        <f>D18/$H18</f>
+        <v>9.650973858237764E-3</v>
+      </c>
+      <c r="J18" s="6">
+        <f t="shared" si="3"/>
+        <v>3.2336876646095582E-3</v>
+      </c>
+      <c r="K18" s="6">
+        <f t="shared" si="4"/>
+        <v>6.7242997319473651E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>14235.644965237007</v>
+      </c>
+      <c r="D19">
+        <v>12011.359570447472</v>
+      </c>
+      <c r="E19">
+        <v>3904.6602134723216</v>
+      </c>
+      <c r="F19">
+        <v>8471.1098315506242</v>
+      </c>
+      <c r="H19">
+        <v>966032.36495268077</v>
+      </c>
+      <c r="I19" s="6">
+        <f>D19/$H19</f>
+        <v>1.243370305821568E-2</v>
+      </c>
+      <c r="J19" s="6">
+        <f t="shared" si="3"/>
+        <v>4.0419558962329219E-3</v>
+      </c>
+      <c r="K19" s="6">
+        <f t="shared" si="4"/>
+        <v>8.7689710395630113E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>18274.91745403735</v>
+      </c>
+      <c r="D20">
+        <v>15465.186894638115</v>
+      </c>
+      <c r="E20">
+        <v>5075.9672550456598</v>
+      </c>
+      <c r="F20">
+        <v>10875.454642435099</v>
+      </c>
+      <c r="H20">
+        <v>1021838.2872890724</v>
+      </c>
+      <c r="I20" s="6">
+        <f>D20/$H20</f>
+        <v>1.5134671588463487E-2</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="3"/>
+        <v>4.9674858714798742E-3</v>
+      </c>
+      <c r="K20" s="6">
+        <f t="shared" si="4"/>
+        <v>1.0643029114995858E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>22722.553800688824</v>
+      </c>
+      <c r="D21">
+        <v>19271.803757165326</v>
+      </c>
+      <c r="E21">
+        <v>6388.3659730677027</v>
+      </c>
+      <c r="F21">
+        <v>13489.591794248059</v>
+      </c>
+      <c r="H21">
+        <v>1080552.5805097325</v>
+      </c>
+      <c r="I21" s="6">
+        <f>D21/$H21</f>
+        <v>1.7835137414668131E-2</v>
+      </c>
+      <c r="J21" s="6">
+        <f t="shared" si="3"/>
+        <v>5.9121287462513845E-3</v>
+      </c>
+      <c r="K21" s="6">
+        <f t="shared" si="4"/>
+        <v>1.2483975363683432E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>27617.607446484035</v>
+      </c>
+      <c r="D22">
+        <v>23469.718182633398</v>
+      </c>
+      <c r="E22">
+        <v>7873.472359663574</v>
+      </c>
+      <c r="F22">
+        <v>16335.209777295648</v>
+      </c>
+      <c r="H22">
+        <v>1142744.7296126776</v>
+      </c>
+      <c r="I22" s="6">
+        <f>D22/$H22</f>
+        <v>2.0538023562434837E-2</v>
+      </c>
+      <c r="J22" s="6">
+        <f t="shared" si="3"/>
+        <v>6.8899660227111368E-3</v>
+      </c>
+      <c r="K22" s="6">
+        <f t="shared" si="4"/>
+        <v>1.429471460597531E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>32977.752680797363</v>
+      </c>
+      <c r="D23">
+        <v>28073.332776476862</v>
+      </c>
+      <c r="E23">
+        <v>9530.9569870774867</v>
+      </c>
+      <c r="F23">
+        <v>19427.856422057375</v>
+      </c>
+      <c r="H23">
+        <v>1208046.7824706435</v>
+      </c>
+      <c r="I23" s="6">
+        <f>D23/$H23</f>
+        <v>2.3238613921112004E-2</v>
+      </c>
+      <c r="J23" s="6">
+        <f t="shared" si="3"/>
+        <v>7.8895595148932868E-3</v>
+      </c>
+      <c r="K23" s="6">
+        <f t="shared" si="4"/>
+        <v>1.6082039788495928E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>38870.844760160893</v>
+      </c>
+      <c r="D24">
+        <v>33138.933352821507</v>
+      </c>
+      <c r="E24">
+        <v>11401.805325503694</v>
+      </c>
+      <c r="F24">
+        <v>22783.745218043216</v>
+      </c>
+      <c r="H24">
+        <v>1278062.3353235552</v>
+      </c>
+      <c r="I24" s="6">
+        <f>D24/$H24</f>
+        <v>2.5929043081010624E-2</v>
+      </c>
+      <c r="J24" s="6">
+        <f t="shared" si="3"/>
+        <v>8.9211652752580368E-3</v>
+      </c>
+      <c r="K24" s="6">
+        <f t="shared" si="4"/>
+        <v>1.7826787151407029E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>45293.821970793651</v>
+      </c>
+      <c r="D25">
+        <v>38681.429805724532</v>
+      </c>
+      <c r="E25">
+        <v>13480.825120304013</v>
+      </c>
+      <c r="F25">
+        <v>26424.211282190634</v>
+      </c>
+      <c r="H25">
+        <v>1350470.4846876522</v>
+      </c>
+      <c r="I25" s="6">
+        <f>D25/$H25</f>
+        <v>2.8642928701008291E-2</v>
+      </c>
+      <c r="J25" s="6">
+        <f t="shared" si="3"/>
+        <v>9.9823174761364507E-3</v>
+      </c>
+      <c r="K25" s="6">
+        <f t="shared" si="4"/>
+        <v>1.9566670713504888E-2</v>
       </c>
     </row>
   </sheetData>
@@ -7335,13 +7736,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920354A5-B397-42DE-9145-96BF0D237E77}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>24</v>
       </c>
@@ -7358,7 +7759,7 @@
         <v>12</v>
       </c>
       <c r="H1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I1" t="s">
         <v>10</v>
@@ -7369,8 +7770,11 @@
       <c r="K1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -7402,7 +7806,7 @@
         <v>2.9325865996732577E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -7434,7 +7838,7 @@
         <v>8.9532353255531993E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -7466,7 +7870,7 @@
         <v>1.4981929309199228E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -7498,7 +7902,7 @@
         <v>2.0462475367846535E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -7530,7 +7934,7 @@
         <v>2.6651464190306742E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -7562,7 +7966,7 @@
         <v>3.2310247605906041E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -7594,7 +7998,7 @@
         <v>3.7855970234070967E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -7626,7 +8030,7 @@
         <v>4.3298258395601287E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -7658,7 +8062,7 @@
         <v>4.8658629225703069E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -7690,7 +8094,7 @@
         <v>5.3880048382261937E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -7722,10 +8126,193 @@
         <v>5.9077444851245491E-2</v>
       </c>
     </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G18" t="s">
-        <v>32</v>
-      </c>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I15" s="7">
+        <f>PBO_wage_only!S4+PBO_prod_only!I15</f>
+        <v>1.7135790761589175E-5</v>
+      </c>
+      <c r="J15" s="7">
+        <f>PBO_wage_only!Q4+PBO_prod_only!J15</f>
+        <v>-2.8857482293784451E-3</v>
+      </c>
+      <c r="K15" s="7">
+        <f>PBO_wage_only!R4+PBO_prod_only!K15</f>
+        <v>2.9896560513767777E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I16" s="7">
+        <f>PBO_wage_only!S5+PBO_prod_only!I16</f>
+        <v>3.8668784561534308E-3</v>
+      </c>
+      <c r="J16" s="7">
+        <f>PBO_wage_only!Q5+PBO_prod_only!J16</f>
+        <v>-3.8705291066723074E-3</v>
+      </c>
+      <c r="K16" s="7">
+        <f>PBO_wage_only!R5+PBO_prod_only!K16</f>
+        <v>9.0750908490917492E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I17" s="7">
+        <f>PBO_wage_only!S6+PBO_prod_only!I17</f>
+        <v>7.6294080660966844E-3</v>
+      </c>
+      <c r="J17" s="7">
+        <f>PBO_wage_only!Q6+PBO_prod_only!J17</f>
+        <v>-5.5461724517235746E-3</v>
+      </c>
+      <c r="K17" s="7">
+        <f>PBO_wage_only!R6+PBO_prod_only!K17</f>
+        <v>1.5123695717566173E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I18" s="7">
+        <f>PBO_wage_only!S7+PBO_prod_only!I18</f>
+        <v>1.097526595202354E-2</v>
+      </c>
+      <c r="J18" s="7">
+        <f>PBO_wage_only!Q7+PBO_prod_only!J18</f>
+        <v>-6.9963099077434846E-3</v>
+      </c>
+      <c r="K18" s="7">
+        <f>PBO_wage_only!R7+PBO_prod_only!K18</f>
+        <v>2.0560578454011907E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I19" s="7">
+        <f>PBO_wage_only!S8+PBO_prod_only!I19</f>
+        <v>1.4567901739001977E-2</v>
+      </c>
+      <c r="J19" s="7">
+        <f>PBO_wage_only!Q8+PBO_prod_only!J19</f>
+        <v>-8.9291017944837896E-3</v>
+      </c>
+      <c r="K19" s="7">
+        <f>PBO_wage_only!R8+PBO_prod_only!K19</f>
+        <v>2.6651804939803903E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I20" s="7">
+        <f>PBO_wage_only!S9+PBO_prod_only!I20</f>
+        <v>1.7725272568714263E-2</v>
+      </c>
+      <c r="J20" s="7">
+        <f>PBO_wage_only!Q9+PBO_prod_only!J20</f>
+        <v>-1.0539507100945571E-2</v>
+      </c>
+      <c r="K20" s="7">
+        <f>PBO_wage_only!R9+PBO_prod_only!K20</f>
+        <v>3.2158984920859023E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I21" s="7">
+        <f>PBO_wage_only!S10+PBO_prod_only!I21</f>
+        <v>2.0839409507799018E-2</v>
+      </c>
+      <c r="J21" s="7">
+        <f>PBO_wage_only!Q10+PBO_prod_only!J21</f>
+        <v>-1.2142439665549674E-2</v>
+      </c>
+      <c r="K21" s="7">
+        <f>PBO_wage_only!R10+PBO_prod_only!K21</f>
+        <v>3.7501263206838151E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I22" s="7">
+        <f>PBO_wage_only!S11+PBO_prod_only!I22</f>
+        <v>2.3865691758914384E-2</v>
+      </c>
+      <c r="J22" s="7">
+        <f>PBO_wage_only!Q11+PBO_prod_only!J22</f>
+        <v>-1.369274898190373E-2</v>
+      </c>
+      <c r="K22" s="7">
+        <f>PBO_wage_only!R11+PBO_prod_only!K22</f>
+        <v>4.2690434654307656E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I23" s="7">
+        <f>PBO_wage_only!S12+PBO_prod_only!I23</f>
+        <v>2.6755095529599156E-2</v>
+      </c>
+      <c r="J23" s="7">
+        <f>PBO_wage_only!Q12+PBO_prod_only!J23</f>
+        <v>-1.5261309811372895E-2</v>
+      </c>
+      <c r="K23" s="7">
+        <f>PBO_wage_only!R12+PBO_prod_only!K23</f>
+        <v>4.7749915626899411E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I24" s="7">
+        <f>PBO_wage_only!S13+PBO_prod_only!I24</f>
+        <v>2.9545614761660462E-2</v>
+      </c>
+      <c r="J24" s="7">
+        <f>PBO_wage_only!Q13+PBO_prod_only!J24</f>
+        <v>-1.6763558942860229E-2</v>
+      </c>
+      <c r="K24" s="7">
+        <f>PBO_wage_only!R13+PBO_prod_only!K24</f>
+        <v>5.2625984612095542E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I25" s="7">
+        <f>PBO_wage_only!S14+PBO_prod_only!I25</f>
+        <v>3.2276919921655989E-2</v>
+      </c>
+      <c r="J25" s="7">
+        <f>PBO_wage_only!Q14+PBO_prod_only!J25</f>
+        <v>-1.8260793574818374E-2</v>
+      </c>
+      <c r="K25" s="7">
+        <f>PBO_wage_only!R14+PBO_prod_only!K25</f>
+        <v>5.743312278188021E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+    </row>
+    <row r="27" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+    </row>
+    <row r="28" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+    </row>
+    <row r="29" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7734,7 +8321,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCEB7B5F-D672-40C2-8479-F9D222CE553E}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -8421,7 +9008,428 @@
         <v>5.9896155163376659E-2</v>
       </c>
     </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2028</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="6">
+        <f>PBO_prod_only!J15</f>
+        <v>5.9857646669247099E-4</v>
+      </c>
+      <c r="D35" s="6">
+        <f>PBO_prod_only!K15</f>
+        <v>9.5850572600625317E-4</v>
+      </c>
+      <c r="E35" s="6">
+        <f>PBO_prod_only!I15</f>
+        <v>1.4703101614619808E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2029</v>
+      </c>
+      <c r="B36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="6">
+        <f>PBO_prod_only!J16</f>
+        <v>1.4097132892987342E-3</v>
+      </c>
+      <c r="D36" s="6">
+        <f>PBO_prod_only!K16</f>
+        <v>2.9365482675514955E-3</v>
+      </c>
+      <c r="E36" s="6">
+        <f>PBO_prod_only!I16</f>
+        <v>4.1917982876918756E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2030</v>
+      </c>
+      <c r="B37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="6">
+        <f>PBO_prod_only!J17</f>
+        <v>2.2725016306236962E-3</v>
+      </c>
+      <c r="D37" s="6">
+        <f>PBO_prod_only!K17</f>
+        <v>4.9176100171150153E-3</v>
+      </c>
+      <c r="E37" s="6">
+        <f>PBO_prod_only!I17</f>
+        <v>6.964230529849489E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2031</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="6">
+        <f>PBO_prod_only!J18</f>
+        <v>3.2336876646095582E-3</v>
+      </c>
+      <c r="D38" s="6">
+        <f>PBO_prod_only!K18</f>
+        <v>6.7242997319473651E-3</v>
+      </c>
+      <c r="E38" s="6">
+        <f>PBO_prod_only!I18</f>
+        <v>9.650973858237764E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2032</v>
+      </c>
+      <c r="B39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="6">
+        <f>PBO_prod_only!J19</f>
+        <v>4.0419558962329219E-3</v>
+      </c>
+      <c r="D39" s="6">
+        <f>PBO_prod_only!K19</f>
+        <v>8.7689710395630113E-3</v>
+      </c>
+      <c r="E39" s="6">
+        <f>PBO_prod_only!I19</f>
+        <v>1.243370305821568E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2033</v>
+      </c>
+      <c r="B40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="6">
+        <f>PBO_prod_only!J20</f>
+        <v>4.9674858714798742E-3</v>
+      </c>
+      <c r="D40" s="6">
+        <f>PBO_prod_only!K20</f>
+        <v>1.0643029114995858E-2</v>
+      </c>
+      <c r="E40" s="6">
+        <f>PBO_prod_only!I20</f>
+        <v>1.5134671588463487E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2034</v>
+      </c>
+      <c r="B41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="6">
+        <f>PBO_prod_only!J21</f>
+        <v>5.9121287462513845E-3</v>
+      </c>
+      <c r="D41" s="6">
+        <f>PBO_prod_only!K21</f>
+        <v>1.2483975363683432E-2</v>
+      </c>
+      <c r="E41" s="6">
+        <f>PBO_prod_only!I21</f>
+        <v>1.7835137414668131E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2035</v>
+      </c>
+      <c r="B42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="6">
+        <f>PBO_prod_only!J22</f>
+        <v>6.8899660227111368E-3</v>
+      </c>
+      <c r="D42" s="6">
+        <f>PBO_prod_only!K22</f>
+        <v>1.429471460597531E-2</v>
+      </c>
+      <c r="E42" s="6">
+        <f>PBO_prod_only!I22</f>
+        <v>2.0538023562434837E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2036</v>
+      </c>
+      <c r="B43" t="s">
+        <v>36</v>
+      </c>
+      <c r="C43" s="6">
+        <f>PBO_prod_only!J23</f>
+        <v>7.8895595148932868E-3</v>
+      </c>
+      <c r="D43" s="6">
+        <f>PBO_prod_only!K23</f>
+        <v>1.6082039788495928E-2</v>
+      </c>
+      <c r="E43" s="6">
+        <f>PBO_prod_only!I23</f>
+        <v>2.3238613921112004E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2037</v>
+      </c>
+      <c r="B44" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="6">
+        <f>PBO_prod_only!J24</f>
+        <v>8.9211652752580368E-3</v>
+      </c>
+      <c r="D44" s="6">
+        <f>PBO_prod_only!K24</f>
+        <v>1.7826787151407029E-2</v>
+      </c>
+      <c r="E44" s="6">
+        <f>PBO_prod_only!I24</f>
+        <v>2.5929043081010624E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2027</v>
+      </c>
+      <c r="B45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="6">
+        <f>PBO_prod_wage!J15</f>
+        <v>-2.8857482293784451E-3</v>
+      </c>
+      <c r="D45" s="6">
+        <f>PBO_prod_wage!K15</f>
+        <v>2.9896560513767777E-3</v>
+      </c>
+      <c r="E45" s="6">
+        <f>PBO_prod_wage!I15</f>
+        <v>1.7135790761589175E-5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2028</v>
+      </c>
+      <c r="B46" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="6">
+        <f>PBO_prod_wage!J16</f>
+        <v>-3.8705291066723074E-3</v>
+      </c>
+      <c r="D46" s="6">
+        <f>PBO_prod_wage!K16</f>
+        <v>9.0750908490917492E-3</v>
+      </c>
+      <c r="E46" s="6">
+        <f>PBO_prod_wage!I16</f>
+        <v>3.8668784561534308E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2029</v>
+      </c>
+      <c r="B47" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="6">
+        <f>PBO_prod_wage!J17</f>
+        <v>-5.5461724517235746E-3</v>
+      </c>
+      <c r="D47" s="6">
+        <f>PBO_prod_wage!K17</f>
+        <v>1.5123695717566173E-2</v>
+      </c>
+      <c r="E47" s="6">
+        <f>PBO_prod_wage!I17</f>
+        <v>7.6294080660966844E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2030</v>
+      </c>
+      <c r="B48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48" s="6">
+        <f>PBO_prod_wage!J18</f>
+        <v>-6.9963099077434846E-3</v>
+      </c>
+      <c r="D48" s="6">
+        <f>PBO_prod_wage!K18</f>
+        <v>2.0560578454011907E-2</v>
+      </c>
+      <c r="E48" s="6">
+        <f>PBO_prod_wage!I18</f>
+        <v>1.097526595202354E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2031</v>
+      </c>
+      <c r="B49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="6">
+        <f>PBO_prod_wage!J19</f>
+        <v>-8.9291017944837896E-3</v>
+      </c>
+      <c r="D49" s="6">
+        <f>PBO_prod_wage!K19</f>
+        <v>2.6651804939803903E-2</v>
+      </c>
+      <c r="E49" s="6">
+        <f>PBO_prod_wage!I19</f>
+        <v>1.4567901739001977E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2032</v>
+      </c>
+      <c r="B50" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="6">
+        <f>PBO_prod_wage!J20</f>
+        <v>-1.0539507100945571E-2</v>
+      </c>
+      <c r="D50" s="6">
+        <f>PBO_prod_wage!K20</f>
+        <v>3.2158984920859023E-2</v>
+      </c>
+      <c r="E50" s="6">
+        <f>PBO_prod_wage!I20</f>
+        <v>1.7725272568714263E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2033</v>
+      </c>
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" s="6">
+        <f>PBO_prod_wage!J21</f>
+        <v>-1.2142439665549674E-2</v>
+      </c>
+      <c r="D51" s="6">
+        <f>PBO_prod_wage!K21</f>
+        <v>3.7501263206838151E-2</v>
+      </c>
+      <c r="E51" s="6">
+        <f>PBO_prod_wage!I21</f>
+        <v>2.0839409507799018E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2034</v>
+      </c>
+      <c r="B52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="6">
+        <f>PBO_prod_wage!J22</f>
+        <v>-1.369274898190373E-2</v>
+      </c>
+      <c r="D52" s="6">
+        <f>PBO_prod_wage!K22</f>
+        <v>4.2690434654307656E-2</v>
+      </c>
+      <c r="E52" s="6">
+        <f>PBO_prod_wage!I22</f>
+        <v>2.3865691758914384E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2035</v>
+      </c>
+      <c r="B53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="6">
+        <f>PBO_prod_wage!J23</f>
+        <v>-1.5261309811372895E-2</v>
+      </c>
+      <c r="D53" s="6">
+        <f>PBO_prod_wage!K23</f>
+        <v>4.7749915626899411E-2</v>
+      </c>
+      <c r="E53" s="6">
+        <f>PBO_prod_wage!I23</f>
+        <v>2.6755095529599156E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>2036</v>
+      </c>
+      <c r="B54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="6">
+        <f>PBO_prod_wage!J24</f>
+        <v>-1.6763558942860229E-2</v>
+      </c>
+      <c r="D54" s="6">
+        <f>PBO_prod_wage!K24</f>
+        <v>5.2625984612095542E-2</v>
+      </c>
+      <c r="E54" s="6">
+        <f>PBO_prod_wage!I24</f>
+        <v>2.9545614761660462E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2037</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55" s="6">
+        <f>PBO_prod_wage!J25</f>
+        <v>-1.8260793574818374E-2</v>
+      </c>
+      <c r="D55" s="6">
+        <f>PBO_prod_wage!K25</f>
+        <v>5.743312278188021E-2</v>
+      </c>
+      <c r="E55" s="6">
+        <f>PBO_prod_wage!I25</f>
+        <v>3.2276919921655989E-2</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>